--- a/mejores_hiperparametros_xgboost.xlsx
+++ b/mejores_hiperparametros_xgboost.xlsx
@@ -445,19 +445,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03353833527795712</v>
+        <v>0.04714558324780109</v>
       </c>
       <c r="D2" t="n">
-        <v>0.738517149839486</v>
+        <v>0.143217730057101</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9892417775546071</v>
+        <v>0.9940841222253399</v>
       </c>
     </row>
   </sheetData>

--- a/mejores_hiperparametros_xgboost.xlsx
+++ b/mejores_hiperparametros_xgboost.xlsx
@@ -445,19 +445,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04714558324780109</v>
+        <v>0.2318382428711447</v>
       </c>
       <c r="D2" t="n">
-        <v>0.143217730057101</v>
+        <v>0.40177526180696</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9940841222253399</v>
+        <v>0.9939798555626117</v>
       </c>
     </row>
   </sheetData>

--- a/mejores_hiperparametros_xgboost.xlsx
+++ b/mejores_hiperparametros_xgboost.xlsx
@@ -445,19 +445,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2318382428711447</v>
+        <v>0.2913393912350149</v>
       </c>
       <c r="D2" t="n">
-        <v>0.40177526180696</v>
+        <v>0.9936604045300514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9939798555626117</v>
+        <v>0.9939074891819645</v>
       </c>
     </row>
   </sheetData>

--- a/mejores_hiperparametros_xgboost.xlsx
+++ b/mejores_hiperparametros_xgboost.xlsx
@@ -445,19 +445,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2913393912350149</v>
+        <v>0.2382937481066518</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9936604045300514</v>
+        <v>0.9173775849675021</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9939074891819645</v>
+        <v>0.993766965485667</v>
       </c>
     </row>
   </sheetData>
